--- a/01_Investment_Banking/companies/ACME.xlsx
+++ b/01_Investment_Banking/companies/ACME.xlsx
@@ -618,119 +618,119 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
